--- a/public/sample-donors.xlsx
+++ b/public/sample-donors.xlsx
@@ -1,41 +1,83 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView xWindow="390" yWindow="555" windowWidth="17895" windowHeight="6090"/>
+  </bookViews>
   <sheets>
     <sheet name="Donors" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>PAN Card No</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Rahul Sharma</t>
+  </si>
+  <si>
+    <t>Mumbai, Maharashtra</t>
+  </si>
+  <si>
+    <t>ABCDE1234F</t>
+  </si>
+  <si>
+    <t>Priya Patel</t>
+  </si>
+  <si>
+    <t>Ahmedabad, Gujarat</t>
+  </si>
+  <si>
+    <t>FGHIJ5678K</t>
+  </si>
+  <si>
+    <t>Amit Singh</t>
+  </si>
+  <si>
+    <t>New Delhi, Delhi</t>
+  </si>
+  <si>
+    <t>KLMNO9012L</t>
+  </si>
+  <si>
+    <t>Sneha Reddy</t>
+  </si>
+  <si>
+    <t>Hyderabad, Telangana</t>
+  </si>
+  <si>
+    <t>PQRST3456M</t>
+  </si>
+  <si>
+    <t>Vikram Joshi</t>
+  </si>
+  <si>
+    <t>Pune, Maharashtra</t>
+  </si>
+  <si>
+    <t>UVWXY7890N</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -72,6 +114,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,96 +443,103 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="2" max="2" width="31.75" customWidth="1"/>
+    <col min="3" max="3" width="19.25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Full Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Address</v>
-      </c>
-      <c r="C1" t="str">
-        <v>PAN Card No</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Amount</v>
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Rahul Sharma</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Mumbai, Maharashtra</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ABCDE1234F</v>
+    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
       </c>
       <c r="D2">
         <v>5000</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Priya Patel</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Ahmedabad, Gujarat</v>
-      </c>
-      <c r="C3" t="str">
-        <v>FGHIJ5678K</v>
+    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
       </c>
       <c r="D3">
         <v>12000</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Amit Singh</v>
-      </c>
-      <c r="B4" t="str">
-        <v>New Delhi, Delhi</v>
-      </c>
-      <c r="C4" t="str">
-        <v>KLMNO9012L</v>
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
       <c r="D4">
         <v>2500</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Sneha Reddy</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Hyderabad, Telangana</v>
-      </c>
-      <c r="C5" t="str">
-        <v>PQRST3456M</v>
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
       </c>
       <c r="D5">
         <v>100000</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Vikram Joshi</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Pune, Maharashtra</v>
-      </c>
-      <c r="C6" t="str">
-        <v>UVWXY7890N</v>
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
       </c>
       <c r="D6">
         <v>75000</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError sqref="A1:D4 A6:D6 A5:B5 D5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>